--- a/out/LSTM-Mamba1_repeat_4_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.963731762464158e-05</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09148798219401852</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09163800591905182</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2530934911980691</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4150349252481531</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01803285810938519</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1976011605290549</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03162336062868121</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2428092626329469</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03841896026112867</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2880205568831893</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01016583069642506</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2698851613265211</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00564593820742671</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.271002803377555</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01186542279913992</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2890954051100633</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004658844527235129</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2865368090947766</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003315500135208684</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2885087476204461</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001302649224488308</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2877942353802803</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007364197333315546</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2879652060699321</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002780229845942949</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.287782696955001</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001271152532099407</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2877598048645896</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.343951766123847e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.28771916383296</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2876939665716879</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.154786274885033e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2876889554020574</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2876845370680047</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2876810029707528</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2876757071407486</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2876700451437449</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2876698614012858</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2876698981497774</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.287670008395253</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2876700818922366</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2876702656346958</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2876718090713523</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2876732790110254</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2876745284597473</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2876758881539446</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2876736832444354</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2876732790110254</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2876729850230906</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2876726542866642</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2876723602987297</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2876719928138114</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2876718825683359</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2876718458198442</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2876719928138114</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2876715150834178</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.287672470544205</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.287672103059287</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2876725440411889</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2876719193168278</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2876717355743686</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2876713313409586</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2876704861256466</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2876704493771549</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2876705963711222</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2876705228741385</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2876705963711222</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2876706331196141</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2876705228741385</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2876709638560405</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2876708536105649</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.287670816862073</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2876707433650894</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2876707066165977</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2876704861256466</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.287670412628663</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2876703391316794</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2876703758801713</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2876702656346958</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2876703758801713</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2876706698681058</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.00677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.00677127013091</v>
+        <v>1.336187288701382</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.963731762464158e-05</v>
+        <v>-8.981685495295096e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09148798219401852</v>
+        <v>-0.1031823154238629</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09156761951164319</v>
+        <v>-0.1032721322788158</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09163800591905182</v>
+        <v>-0.1033517066653099</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2530934911980691</v>
+        <v>0.2861311147665871</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4150349252481531</v>
+        <v>0.4694604195648643</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01803285810938519</v>
+        <v>0.02038681843846299</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1976011605290549</v>
+        <v>0.2236434416442821</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03162336062868121</v>
+        <v>0.03575140500189955</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2428092626329469</v>
+        <v>0.2747528865943095</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03841896026112867</v>
+        <v>0.04343373486988355</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2880205568831893</v>
+        <v>0.3258659170519456</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01016583069642506</v>
+        <v>0.01149376710483348</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2698851613265211</v>
+        <v>0.3053636910388214</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00564593820742671</v>
+        <v>0.006383352074655672</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.271002803377555</v>
+        <v>0.306627867957063</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01186542279913992</v>
+        <v>0.01341608444515145</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2890954051100633</v>
+        <v>0.3270832730048702</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004658844527235129</v>
+        <v>0.005266803486641007</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2865368090947766</v>
+        <v>0.3241914703249116</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003315500135208684</v>
+        <v>0.003750183789272366</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2885087476204461</v>
+        <v>0.3264216262469106</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001302649224488308</v>
+        <v>0.001472385624344007</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2877942353802803</v>
+        <v>0.3256146499174438</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007364197333315546</v>
+        <v>0.0008335287628531514</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2879652060699321</v>
+        <v>0.3258086446771019</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002780229845942949</v>
+        <v>0.0003144284307454283</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.287782696955001</v>
+        <v>0.325602934954585</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001271152532099407</v>
+        <v>0.0001447306203045994</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2877598048645896</v>
+        <v>0.3255776670517165</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.343951766123847e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.28771916383296</v>
+        <v>0.3255323130809273</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2876939665716879</v>
+        <v>0.3255044669496759</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.154786274885033e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2876889554020574</v>
+        <v>0.3254994542907614</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2876845370680047</v>
+        <v>0.325495108664952</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2876810029707528</v>
+        <v>0.3254917583101592</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2876757071407486</v>
+        <v>0.3254863889831714</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2876700451437449</v>
+        <v>0.3254803962497411</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2876698614012858</v>
+        <v>0.3254750284611627</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2876698981497774</v>
+        <v>0.3254750652096544</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.287670008395253</v>
+        <v>0.3254751754551299</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2876700818922366</v>
+        <v>0.3254752489521135</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2876702656346958</v>
+        <v>0.3254754326945727</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2876718090713523</v>
+        <v>0.3254769761312292</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2876732790110254</v>
+        <v>0.3254784460709023</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2876745284597473</v>
+        <v>0.3254796955196243</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2876758881539446</v>
+        <v>0.3254810552138216</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2876736832444354</v>
+        <v>0.3254788503043123</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2876732790110254</v>
+        <v>0.3254784460709023</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3254776008555903</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2876729850230906</v>
+        <v>0.3254781520829676</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2876726542866642</v>
+        <v>0.3254778213465412</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2876723602987297</v>
+        <v>0.3254775273586067</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3254776008555903</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2876719928138114</v>
+        <v>0.3254771598736884</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2876718825683359</v>
+        <v>0.3254770496282128</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2876718458198442</v>
+        <v>0.3254770128797211</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2876719928138114</v>
+        <v>0.3254771598736884</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2876715150834178</v>
+        <v>0.3254766821432947</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.287672470544205</v>
+        <v>0.325477637604082</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2876724337957133</v>
+        <v>0.3254776008555903</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.287672103059287</v>
+        <v>0.3254772701191639</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2876725440411889</v>
+        <v>0.3254777111010659</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2876719193168278</v>
+        <v>0.3254770863767047</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2876717355743686</v>
+        <v>0.3254769026342456</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2876713313409586</v>
+        <v>0.3254764984008355</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2876704861256466</v>
+        <v>0.3254756531855236</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2876704493771549</v>
+        <v>0.3254756164370319</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2876705963711222</v>
+        <v>0.3254757634309991</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2876705228741385</v>
+        <v>0.3254756899340155</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2876705963711222</v>
+        <v>0.3254757634309991</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2876706331196141</v>
+        <v>0.3254758001794911</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2876705228741385</v>
+        <v>0.3254756899340155</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2876709638560405</v>
+        <v>0.3254761309159175</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2876708536105649</v>
+        <v>0.3254760206704419</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.287670816862073</v>
+        <v>0.32547598392195</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2876707433650894</v>
+        <v>0.3254759104249664</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2876707066165977</v>
+        <v>0.3254758736764747</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2876704861256466</v>
+        <v>0.3254756531855236</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.287670412628663</v>
+        <v>0.32547557968854</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2876703391316794</v>
+        <v>0.3254755061915564</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2876703758801713</v>
+        <v>0.3254755429400483</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2876702656346958</v>
+        <v>0.3254754326945727</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2876703758801713</v>
+        <v>0.3254755429400483</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2876706698681058</v>
+        <v>0.3254758369279828</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002014285419136286</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.44</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001323465607129037</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0009524016641080379</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0008582700975239277</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.000782018294557929</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0006709287408739328</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0005636976566165686</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0004748816136270761</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0003997660242021084</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0003222108352929354</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0002508300822228193</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.000215419102460146</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0001863392535597086</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0001781224273145199</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0002119368873536587</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0002271384000778198</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0001994303893297911</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001488262787461281</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-8.47838819026947e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-2.42237001657486e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>2.251542173326015e-05</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.536187288701382</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>7.165549322962761e-05</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0001080704387277365</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0001320636365562677</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0001381298061460257</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0001571706961840391</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0001799622550606728</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0002056991215795279</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0002174340188503265</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0002172929234802723</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.427500299518339</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0001618957612663507</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.227500299518339</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>9.707780554890633e-05</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>7.545994594693184e-05</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>5.878228694200516e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>4.721293225884438e-05</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>5.329190753400326e-05</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>4.303152672946453e-05</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>3.826082684099674e-05</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>3.006821498274803e-05</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.336187288701382</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-2.816133201122284e-05</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-9.805732406675816e-05</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0002037372905761003</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0003768845926970243</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0006856224499642849</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.981685495295096e-05</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1031823154238629</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0009224098175764084</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0009912764653563499</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001008953433483839</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0009629866108298302</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0009077910799533129</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0008378336206078529</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0007868059910833836</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0007431984413415194</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0007473246660083532</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0007690484635531902</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.000812202924862504</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0008617164567112923</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0009230636060237885</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1032721322788158</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.00103357108309865</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1033517066653099</v>
+        <v>-0.08882259802308166</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2861311147665871</v>
+        <v>0.2450100850180599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001191866234876215</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4694604195648643</v>
+        <v>0.4016685148271203</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02038681843846299</v>
+        <v>0.01745691711621853</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00128439930267632</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2236434416442821</v>
+        <v>0.191178799990556</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03575140500189955</v>
+        <v>0.03061348468161163</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001382047194056213</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2747528865943095</v>
+        <v>0.2349432102014082</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04343373486988355</v>
+        <v>0.03719176846430827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00149740872438997</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3258659170519456</v>
+        <v>0.2787107170440257</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01149376710483348</v>
+        <v>0.009841275378308329</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001549955457448959</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3053636910388214</v>
+        <v>0.2611541543437242</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006383352074655672</v>
+        <v>0.005465436902612457</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001611613086424768</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.306627867957063</v>
+        <v>0.2622359371537592</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01341608444515145</v>
+        <v>0.01148623516005559</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001821005949750543</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3270832730048702</v>
+        <v>0.2797504684094372</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005266803486641007</v>
+        <v>0.004509882471444446</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002030643634498119</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3241914703249116</v>
+        <v>0.2772734336275656</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003750183789272366</v>
+        <v>0.00321027909196311</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002242635004222393</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3264216262469106</v>
+        <v>0.2791822281331267</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001472385624344007</v>
+        <v>0.001260554597324094</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002374672330915928</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3256146499174438</v>
+        <v>0.2784905558508476</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008335287628531514</v>
+        <v>0.0007132985358264126</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002462638774886727</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3258086446771019</v>
+        <v>0.27865586087661</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003144284307454283</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002458723727613688</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.325602934954585</v>
+        <v>0.2784792441804321</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001447306203045994</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002394822891801596</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3255776670517165</v>
+        <v>0.2784569460431346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.989812001607026e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002268255455419421</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3255323130809273</v>
+        <v>0.278417483246295</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.121751555640607e-05</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00210519228130579</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3255044669496759</v>
+        <v>0.2783929482025178</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.108757778203038e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.001960520166903734</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3254994542907614</v>
+        <v>0.278387937032887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001877933158539236</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.325495108664952</v>
+        <v>0.2783834827390828</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001853820751421154</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3254917583101592</v>
+        <v>0.2783799486418308</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001826114254072309</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3254863889831714</v>
+        <v>0.2783746528118267</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001742813852615654</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3254803962497411</v>
+        <v>0.278368990814823</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001648274599574506</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3254750284611627</v>
+        <v>0.2783688070723638</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001559001742862165</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3254750652096544</v>
+        <v>0.2783688438208555</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001523353974334896</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3254751754551299</v>
+        <v>0.2783689540663311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001523099723272026</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3254752489521135</v>
+        <v>0.2783690275633147</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001600311021320522</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3254754326945727</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001887824852019548</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3254769761312292</v>
+        <v>0.2783707547424303</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002413792768493295</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3254784460709023</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003071247600018978</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3254796955196243</v>
+        <v>0.2783734741308254</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003665472380816936</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3254810552138216</v>
+        <v>0.2783748338250227</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.004038584884256124</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3254788503043123</v>
+        <v>0.2783726289155134</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004148455336689949</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3254784460709023</v>
+        <v>0.2783722246821034</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004101587459445</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3254776008555903</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.004055421333760023</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3254781520829676</v>
+        <v>0.2783719306941687</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003976976498961449</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3254778213465412</v>
+        <v>0.2783715999577422</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003871267195791006</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3254775273586067</v>
+        <v>0.2783713059698078</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003760022344067693</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3254776008555903</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003611373482272029</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3254771598736884</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003468045266345143</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3254770496282128</v>
+        <v>0.2783708282394139</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003357485868036747</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3254770128797211</v>
+        <v>0.2783707914909222</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.003260234370827675</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3254771598736884</v>
+        <v>0.2783709384848895</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00316741643473506</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3254766821432947</v>
+        <v>0.2783704607544958</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003236779477447271</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.325477637604082</v>
+        <v>0.2783714162152831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003332438413053751</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3254776008555903</v>
+        <v>0.2783713794667914</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003375228494405746</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3254772701191639</v>
+        <v>0.278371048730365</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003408608259633183</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3254777111010659</v>
+        <v>0.2783714897122669</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003353075357154012</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3254770863767047</v>
+        <v>0.2783708649879058</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003229431807994843</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3254769026342456</v>
+        <v>0.2783706812454467</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003033771412447095</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3254764984008355</v>
+        <v>0.2783702770120366</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002750607207417488</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3254756531855236</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002490839920938015</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3254756164370319</v>
+        <v>0.278369395048233</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002307018032297492</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3254757634309991</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002188229467719793</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3254756899340155</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002135663758963346</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3254757634309991</v>
+        <v>0.2783695420422002</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002110933419317007</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3254758001794911</v>
+        <v>0.2783695787906921</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002094726776704192</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3254756899340155</v>
+        <v>0.2783694685452166</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002140473574399948</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3254761309159175</v>
+        <v>0.2783699095271185</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002177131362259388</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3254760206704419</v>
+        <v>0.278369799281643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002195727778598666</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.32547598392195</v>
+        <v>0.2783697625331511</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002185418270528316</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3254759104249664</v>
+        <v>0.2783696890361674</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.00215239217504859</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3254758736764747</v>
+        <v>0.2783696522876757</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002081709681078792</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3254756531855236</v>
+        <v>0.2783694317967247</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002005412708967924</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.32547557968854</v>
+        <v>0.2783693582997411</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001929642865434289</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3254755061915564</v>
+        <v>0.2783692848027574</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001872852561064065</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3254755429400483</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001820831326767802</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3254754326945727</v>
+        <v>0.2783692113057738</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.001825578860007226</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3254755429400483</v>
+        <v>0.2783693215512494</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001896672532893717</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3254758369279828</v>
+        <v>0.2783696155391838</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_4_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.002014285419136286</v>
+        <v>-0.002014284487813711</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.44</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.001323465607129037</v>
+        <v>-0.001323460950516164</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.16</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.0009524016641080379</v>
+        <v>-0.0009523998014628887</v>
       </c>
       <c r="JB4" t="n">
         <v>0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.0008582700975239277</v>
+        <v>-0.000858269864693284</v>
       </c>
       <c r="JB5" t="n">
         <v>0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.000782018294557929</v>
+        <v>-0.0007820180617272854</v>
       </c>
       <c r="JB6" t="n">
         <v>0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0006709287408739328</v>
+        <v>-0.0006709292065352201</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0005636976566165686</v>
+        <v>-0.0005636939313262701</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0004748816136270761</v>
+        <v>-0.0004748809151351452</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0003997660242021084</v>
+        <v>-0.0003997657913714647</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0003222108352929354</v>
+        <v>-0.0003222017548978329</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0002508300822228193</v>
+        <v>-0.0002508254256099463</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.000215419102460146</v>
+        <v>-0.0002154165413230658</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0001863392535597086</v>
+        <v>-0.0001863311044871807</v>
       </c>
       <c r="JB14" t="n">
         <v>0.3999999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0001781224273145199</v>
+        <v>-0.0001781207975000143</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3999999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0002119368873536587</v>
+        <v>-0.0002119359560310841</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0001994303893297911</v>
+        <v>-0.0001994320191442966</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0001488262787461281</v>
+        <v>-0.0001488267444074154</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-8.47838819026947e-05</v>
+        <v>-8.478481322526932e-05</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-2.42237001657486e-05</v>
+        <v>-2.422230318188667e-05</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>2.251542173326015e-05</v>
+        <v>2.2512162104249e-05</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>7.165549322962761e-05</v>
+        <v>7.165526039898396e-05</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3999999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0001080704387277365</v>
+        <v>0.0001080683432519436</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3999999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0001320636365562677</v>
+        <v>0.0001320673618465662</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3999999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0001381298061460257</v>
+        <v>0.0001381414476782084</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3999999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0001571706961840391</v>
+        <v>0.0001571786124259233</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3999999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.0001799622550606728</v>
+        <v>0.000179963419213891</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3999999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0002056991215795279</v>
+        <v>0.0002057019155472517</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3999999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.0002174340188503265</v>
+        <v>0.0002174347173422575</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3999999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0002172929234802723</v>
+        <v>0.0002172954846173525</v>
       </c>
       <c r="JB31" t="n">
         <v>0.2599999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.0001618957612663507</v>
+        <v>0.0001618945971131325</v>
       </c>
       <c r="JB32" t="n">
         <v>0.1199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>9.707780554890633e-05</v>
+        <v>9.707664139568806e-05</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.02000000000000007</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>7.545994594693184e-05</v>
+        <v>7.545924745500088e-05</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>5.878228694200516e-05</v>
+        <v>5.878135561943054e-05</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>5.329190753400326e-05</v>
+        <v>5.328911356627941e-05</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>4.303152672946453e-05</v>
+        <v>4.302873276174068e-05</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>3.826082684099674e-05</v>
+        <v>3.825710155069828e-05</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>3.006821498274803e-05</v>
+        <v>3.006518818438053e-05</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-2.816133201122284e-05</v>
+        <v>-2.815993502736092e-05</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.5799999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-9.805732406675816e-05</v>
+        <v>-9.805615991353989e-05</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0002037372905761003</v>
+        <v>-0.0002037377562373877</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0003768845926970243</v>
+        <v>-0.0003768852911889553</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0006856224499642849</v>
+        <v>-0.0006856231484562159</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0009224098175764084</v>
+        <v>-0.0009224123787134886</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0009912764653563499</v>
+        <v>-0.0009912755340337753</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001008953433483839</v>
+        <v>-0.001008955296128988</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0009629866108298302</v>
+        <v>-0.0009629880078136921</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.0009077910799533129</v>
+        <v>-0.0009077931754291058</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0008378336206078529</v>
+        <v>-0.0008378357160836458</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0007868059910833836</v>
+        <v>-0.0007868085522204638</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0007431984413415194</v>
+        <v>-0.0007431998383253813</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0007473246660083532</v>
+        <v>-0.0007473248988389969</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0007690484635531902</v>
+        <v>-0.0007690491620451212</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.000812202924862504</v>
+        <v>-0.0008122031576931477</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0008617164567112923</v>
+        <v>-0.0008617150597274303</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0009230636060237885</v>
+        <v>-0.0009230631403625011</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001191866234876215</v>
+        <v>-0.001191868679597974</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.00128439930267632</v>
+        <v>-0.001284400001168251</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001382047194056213</v>
+        <v>-0.001382046495564282</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.00149740872438997</v>
+        <v>-0.001497407094575465</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001549955457448959</v>
+        <v>-0.001549955690279603</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001611613086424768</v>
+        <v>-0.001611613901332021</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.001821005949750543</v>
+        <v>-0.00182100513484329</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002030643634498119</v>
+        <v>-0.002030647359788418</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002242635004222393</v>
+        <v>-0.002242643851786852</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.002374672330915928</v>
+        <v>-0.002374677453190088</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002462638774886727</v>
+        <v>-0.002462644828483462</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.002458723727613688</v>
+        <v>-0.002458730945363641</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002394822891801596</v>
+        <v>-0.002394829876720905</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002268255455419421</v>
+        <v>-0.0022682617418468</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.00210519228130579</v>
+        <v>-0.002105198334902525</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.001960520166903734</v>
+        <v>-0.001960522495210171</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001877933158539236</v>
+        <v>-0.001877934555523098</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001853820751421154</v>
+        <v>-0.001853824593126774</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.001826114254072309</v>
+        <v>-0.00182611879426986</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001742813852615654</v>
+        <v>-0.001742815598845482</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.2599999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001648274599574506</v>
+        <v>-0.001648276811465621</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.001559001742862165</v>
+        <v>-0.001559002790600061</v>
       </c>
       <c r="JB81" t="n">
         <v>0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.001523353974334896</v>
+        <v>-0.00152335490565747</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001523099723272026</v>
+        <v>-0.001523100305348635</v>
       </c>
       <c r="JB83" t="n">
         <v>0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.001600311021320522</v>
+        <v>-0.001600312534719706</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001887824852019548</v>
+        <v>-0.001887826714664698</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002413792768493295</v>
+        <v>-0.002413794165477157</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003071247600018978</v>
+        <v>-0.003071250161156058</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003665472380816936</v>
+        <v>-0.003665474010631442</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.004038584884256124</v>
+        <v>-0.004038566257804632</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.004148455336689949</v>
+        <v>-0.004148446023464203</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.004101587459445</v>
+        <v>-0.004101578146219254</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.004055421333760023</v>
+        <v>-0.004055423196405172</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003976976498961449</v>
+        <v>-0.003976977430284023</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003871267195791006</v>
+        <v>-0.00387127511203289</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003760022344067693</v>
+        <v>-0.003760023042559624</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.003611373482272029</v>
+        <v>-0.003611373249441385</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.003468045266345143</v>
+        <v>-0.003468048758804798</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.003357485868036747</v>
+        <v>-0.003357488196343184</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.003260234370827675</v>
+        <v>-0.003260241588577628</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.00316741643473506</v>
+        <v>-0.003167418763041496</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003236779477447271</v>
+        <v>-0.003236789256334305</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003332438413053751</v>
+        <v>-0.003332441207021475</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003375228494405746</v>
+        <v>-0.003375239204615355</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003408608259633183</v>
+        <v>-0.003408611286431551</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003353075357154012</v>
+        <v>-0.003353077219799161</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.2599999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003229431807994843</v>
+        <v>-0.003229433437809348</v>
       </c>
       <c r="JB106" t="n">
         <v>0.02000000000000007</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003033771412447095</v>
+        <v>-0.003033779561519623</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.002750607207417488</v>
+        <v>-0.002750613028183579</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002490839920938015</v>
+        <v>-0.002490838291123509</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002307018032297492</v>
+        <v>-0.002307015471160412</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002188229467719793</v>
+        <v>-0.002188229933381081</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002135663758963346</v>
+        <v>-0.002135662827640772</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002110933419317007</v>
+        <v>-0.002110933884978294</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002094726776704192</v>
+        <v>-0.002094729337841272</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002140473574399948</v>
+        <v>-0.002140471478924155</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002177131362259388</v>
+        <v>-0.00217712763696909</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002195727778598666</v>
+        <v>-0.002195726148784161</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002185418270528316</v>
+        <v>-0.002185417572036386</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.00215239217504859</v>
+        <v>-0.002152396598830819</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002081709681078792</v>
+        <v>-0.002081711776554585</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002005412708967924</v>
+        <v>-0.002005415270105004</v>
       </c>
       <c r="JB121" t="n">
         <v>0.2599999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.001929642865434289</v>
+        <v>-0.001929644728079438</v>
       </c>
       <c r="JB122" t="n">
         <v>0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001872852561064065</v>
+        <v>-0.001872855238616467</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001820831326767802</v>
+        <v>-0.001820832607336342</v>
       </c>
       <c r="JB124" t="n">
         <v>0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.001825578860007226</v>
+        <v>-0.001825580955483019</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.001896672532893717</v>
+        <v>-0.001896674279123545</v>
       </c>
       <c r="JB126" t="n">
         <v>0.9999999999999996</v>
